--- a/data/raw/inventory/Week 32/Fossil/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 32/Fossil/Seller FBA Inventory (SP-API).xlsx
@@ -2938,10 +2938,10 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F41" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -2956,7 +2956,7 @@
         <v>2</v>
       </c>
       <c r="K41" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -10133,7 +10133,7 @@
         <v>52</v>
       </c>
       <c r="F157" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G157" t="n">
         <v>2</v>
@@ -10145,7 +10145,7 @@
         <v>0</v>
       </c>
       <c r="J157" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K157" t="n">
         <v>54</v>
@@ -10378,7 +10378,7 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F161" t="n">
         <v>2</v>
@@ -10393,10 +10393,10 @@
         <v>0</v>
       </c>
       <c r="J161" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K161" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L161" t="n">
         <v>0</v>
@@ -14411,7 +14411,7 @@
         <v>806</v>
       </c>
       <c r="F226" t="n">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="G226" t="n">
         <v>1</v>
@@ -14423,7 +14423,7 @@
         <v>0</v>
       </c>
       <c r="J226" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K226" t="n">
         <v>807</v>
@@ -14470,7 +14470,7 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F227" t="n">
         <v>10</v>
@@ -14485,10 +14485,10 @@
         <v>0</v>
       </c>
       <c r="J227" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K227" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L227" t="n">
         <v>1</v>
@@ -15400,7 +15400,7 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F242" t="n">
         <v>0</v>
@@ -15415,10 +15415,10 @@
         <v>0</v>
       </c>
       <c r="J242" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K242" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L242" t="n">
         <v>0</v>
@@ -17322,10 +17322,10 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F273" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G273" t="n">
         <v>8</v>
@@ -17340,7 +17340,7 @@
         <v>12</v>
       </c>
       <c r="K273" t="n">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="L273" t="n">
         <v>3</v>
@@ -20859,7 +20859,7 @@
         <v>869</v>
       </c>
       <c r="F330" t="n">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="G330" t="n">
         <v>37</v>
@@ -20871,7 +20871,7 @@
         <v>0</v>
       </c>
       <c r="J330" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K330" t="n">
         <v>874</v>
@@ -20918,10 +20918,10 @@
         </is>
       </c>
       <c r="E331" t="n">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="F331" t="n">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="G331" t="n">
         <v>1</v>
@@ -20933,10 +20933,10 @@
         <v>0</v>
       </c>
       <c r="J331" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K331" t="n">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="L331" t="n">
         <v>0</v>
@@ -21228,10 +21228,10 @@
         </is>
       </c>
       <c r="E336" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F336" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G336" t="n">
         <v>0</v>
@@ -21246,7 +21246,7 @@
         <v>0</v>
       </c>
       <c r="K336" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L336" t="n">
         <v>0</v>
@@ -21417,7 +21417,7 @@
         <v>8</v>
       </c>
       <c r="F339" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G339" t="n">
         <v>0</v>
@@ -21429,7 +21429,7 @@
         <v>0</v>
       </c>
       <c r="J339" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K339" t="n">
         <v>8</v>
@@ -25878,7 +25878,7 @@
         </is>
       </c>
       <c r="E411" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F411" t="n">
         <v>26</v>
@@ -25893,10 +25893,10 @@
         <v>0</v>
       </c>
       <c r="J411" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K411" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L411" t="n">
         <v>0</v>
